--- a/raw_data/实测数据/数据记录.xlsx
+++ b/raw_data/实测数据/数据记录.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86153\Desktop\diploma_project\raw_data\实测数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304964C5-127F-438D-B0A1-24CCAEA9B673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63691A39-6597-43C4-AE00-FC3A3923BD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="2655" windowWidth="21600" windowHeight="11295" xr2:uid="{3B48B130-AF04-4D73-8C0F-E5A0AD9E9E6F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3B48B130-AF04-4D73-8C0F-E5A0AD9E9E6F}"/>
   </bookViews>
   <sheets>
     <sheet name="仿真数据" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>仿真值</t>
   </si>
@@ -64,6 +64,334 @@
   </si>
   <si>
     <t>Q</t>
+  </si>
+  <si>
+    <t>297.65m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>R[Ω]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>L[H]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>915.08n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2053u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>419.73m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.2891u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>327.81m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>801.98n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>264.98m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>646.96n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>352.56m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>976.36n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>206.25m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>529.49n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.0001u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>337.32m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.2886u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>880.01m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>25.118u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.2736u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>841.54m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.7973u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1640u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.7686u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>625.81m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.3943u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.6410u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.6957u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>431.46n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>223.9m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>解析公式计算值</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>232.84n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>120.97m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>528.94n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>202.79m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>450.07n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>139.95m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>525.66n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>210.78m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.4652u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>640.64m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.3499u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>803.60m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.9462u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.5184u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.7918u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.9022u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.5009u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.8702u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>219.32n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>137.56m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>179.76n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>86.578m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.1834u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>775.92m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>393.15n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>132.32m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>980.89n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>277.75m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.4965u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.0985u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>882.25m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.5360u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>543.20n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>217.59m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>774.82n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>226.10m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5939u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>632.48m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.9615u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>518.60m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>555.50n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>189.73m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>412.81n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>201.90m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>245.48n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>98.413m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>641.93n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>204.07m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.1099u</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>243.01m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -413,7 +741,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -666,10 +994,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1042,47 +1370,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4131FE4D-D58B-4251-8C1D-25106ADD5964}">
-  <dimension ref="A1:K63"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N57"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="8.6640625" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="N1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>4</v>
       </c>
@@ -1110,8 +1450,14 @@
       <c r="I3" s="1">
         <v>86.083803979999999</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -1139,8 +1485,14 @@
       <c r="I4" s="1">
         <v>87.985610780000002</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1168,8 +1520,14 @@
       <c r="I5" s="1">
         <v>94.176681419999994</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1197,8 +1555,14 @@
       <c r="I6" s="1">
         <v>98.784244090000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1226,8 +1590,14 @@
       <c r="I7" s="1">
         <v>102.2470718</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1255,8 +1625,14 @@
       <c r="I8" s="1">
         <v>139.36053870000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>4</v>
       </c>
@@ -1284,8 +1660,14 @@
       <c r="I9" s="1">
         <v>121.8116409</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1313,8 +1695,14 @@
       <c r="I10" s="1">
         <v>93.174602289999996</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1342,8 +1730,14 @@
       <c r="I11" s="1">
         <v>102.211814</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1.5207999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>7</v>
       </c>
@@ -1371,8 +1765,14 @@
       <c r="I12" s="1">
         <v>7.3927227489999998</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="K12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" s="1">
+        <v>49.35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -1400,8 +1800,14 @@
       <c r="I14" s="1">
         <v>8.8168313170000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="K14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -1429,8 +1835,14 @@
       <c r="I15" s="1">
         <v>5.5173764810000003</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="K15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -1458,8 +1870,14 @@
       <c r="I16" s="1">
         <v>85.254862779999996</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="K16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -1487,8 +1905,14 @@
       <c r="I17" s="1">
         <v>114.43911319999999</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="K17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -1516,8 +1940,14 @@
       <c r="I18" s="1">
         <v>89.589246169999996</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="K18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -1545,8 +1975,14 @@
       <c r="I19" s="1">
         <v>130.20877830000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="K19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -1574,8 +2010,14 @@
       <c r="I20" s="1">
         <v>142.0338223</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="K20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -1603,1233 +2045,1239 @@
       <c r="I21" s="1">
         <v>102.5266529</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22">
+      <c r="K21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
         <v>3</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="1">
         <v>30</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>1</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>9.9</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>0.6</v>
       </c>
-      <c r="F22">
-        <v>6.78</v>
-      </c>
-      <c r="G22">
+      <c r="F22" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G22" s="1">
         <v>0.30093238700000002</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>0.36028702400000001</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>35.581960359999997</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23">
+      <c r="K22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
         <v>3</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="1">
         <v>40</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <v>1.2</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="1">
         <v>9.9</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>1.2</v>
       </c>
-      <c r="F23">
-        <v>6.78</v>
-      </c>
-      <c r="G23">
+      <c r="F23" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G23" s="1">
         <v>0.49855030700000003</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>0.20871194800000001</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="1">
         <v>101.7586268</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24">
+      <c r="K23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
         <v>3</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="1">
         <v>40</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
         <v>1.4</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>29.9</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>0.8</v>
       </c>
-      <c r="F24">
-        <v>6.78</v>
-      </c>
-      <c r="G24">
+      <c r="F24" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G24" s="1">
         <v>0.398311211</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>0.37315062300000001</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="1">
         <v>45.472404709999999</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25">
+      <c r="K24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
         <v>3</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="1">
         <v>45</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <v>1.8</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>9.9</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1">
         <v>1.2</v>
       </c>
-      <c r="F25">
-        <v>6.78</v>
-      </c>
-      <c r="G25">
+      <c r="F25" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G25" s="1">
         <v>0.52214684899999997</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>0.16807523199999999</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="1">
         <v>132.34224699999999</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26">
+      <c r="K25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
         <v>3</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="1">
         <v>50</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>1.8</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="1">
         <v>29.9</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>1.2</v>
       </c>
-      <c r="F26">
-        <v>6.78</v>
-      </c>
-      <c r="G26">
+      <c r="F26" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G26" s="1">
         <v>0.60386275700000003</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>0.181093175</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="1">
         <v>142.0514671</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27">
+      <c r="K26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
         <v>3</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="1">
         <v>55</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>1.6</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>49.9</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>1</v>
       </c>
-      <c r="F27">
-        <v>6.78</v>
-      </c>
-      <c r="G27">
+      <c r="F27" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G27" s="1">
         <v>0.73533036200000002</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>0.20875734400000001</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="1">
         <v>150.05493989999999</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28">
+      <c r="K27" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
         <v>3</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <v>60</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>1.4</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="1">
         <v>9.9</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>1.2</v>
       </c>
-      <c r="F28">
-        <v>6.78</v>
-      </c>
-      <c r="G28">
+      <c r="F28" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G28" s="1">
         <v>0.93185604300000002</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>0.29370295099999999</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="1">
         <v>135.16058960000001</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29">
+      <c r="K28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
         <v>3</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="1">
         <v>70</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>1.8</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="1">
         <v>49.9</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1">
         <v>0.8</v>
       </c>
-      <c r="F29">
-        <v>6.78</v>
-      </c>
-      <c r="G29">
+      <c r="F29" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G29" s="1">
         <v>1.0631741539999999</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>0.262538357</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="1">
         <v>172.51275419999999</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30">
+      <c r="K29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
         <v>4</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="2">
         <v>45</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="2">
         <v>0.8</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="2">
         <v>89.9</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="2">
         <v>0.8</v>
       </c>
-      <c r="F30">
-        <v>6.78</v>
-      </c>
-      <c r="G30">
+      <c r="F30" s="2">
+        <v>6.78</v>
+      </c>
+      <c r="G30" s="2">
         <v>0.97154763099999997</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="2">
         <v>0.44398856399999997</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="2">
         <v>93.218449539999995</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
         <v>4</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="2">
         <v>55</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="2">
         <v>1.6</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="2">
         <v>49.9</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="2">
         <v>0.4</v>
       </c>
-      <c r="F31">
-        <v>6.78</v>
-      </c>
-      <c r="G31">
+      <c r="F31" s="2">
+        <v>6.78</v>
+      </c>
+      <c r="G31" s="2">
         <v>1.251840533</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="2">
         <v>0.468870499</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="2">
         <v>113.7380199</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
         <v>4</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="2">
         <v>55</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="2">
         <v>1.4</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="2">
         <v>69.900000000000006</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="2">
         <v>1</v>
       </c>
-      <c r="F32">
-        <v>6.78</v>
-      </c>
-      <c r="G32">
+      <c r="F32" s="2">
+        <v>6.78</v>
+      </c>
+      <c r="G32" s="2">
         <v>1.1114784369999999</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="2">
         <v>0.32620402199999998</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="2">
         <v>145.15142109999999</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
         <v>4</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="2">
         <v>60</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="2">
         <v>1.4</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="2">
         <v>9.9</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="2">
         <v>0.4</v>
       </c>
-      <c r="F33">
-        <v>6.78</v>
-      </c>
-      <c r="G33">
+      <c r="F33" s="2">
+        <v>6.78</v>
+      </c>
+      <c r="G33" s="2">
         <v>1.6951933480000001</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="2">
         <v>0.60421065500000004</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="2">
         <v>119.51995530000001</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
         <v>4</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="2">
         <v>60</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="2">
         <v>0.8</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="2">
         <v>49.9</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="2">
         <v>0.4</v>
       </c>
-      <c r="F34">
-        <v>6.78</v>
-      </c>
-      <c r="G34">
+      <c r="F34" s="2">
+        <v>6.78</v>
+      </c>
+      <c r="G34" s="2">
         <v>1.8759349729999999</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="2">
         <v>0.685534058</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="2">
         <v>116.5730894</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
         <v>4</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="2">
         <v>80</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="2">
         <v>1.6</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="2">
         <v>69.900000000000006</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="2">
         <v>1.2</v>
       </c>
-      <c r="F35">
-        <v>6.78</v>
-      </c>
-      <c r="G35">
+      <c r="F35" s="2">
+        <v>6.78</v>
+      </c>
+      <c r="G35" s="2">
         <v>1.9267512689999999</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="2">
         <v>0.47889950799999997</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="2">
         <v>171.39211</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
         <v>4</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="2">
         <v>80</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="2">
         <v>1.6</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="2">
         <v>25</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="2">
         <v>0.4</v>
       </c>
-      <c r="F36">
-        <v>6.78</v>
-      </c>
-      <c r="G36">
+      <c r="F36" s="2">
+        <v>6.78</v>
+      </c>
+      <c r="G36" s="2">
         <v>2.5528820909999999</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="2">
         <v>0.84264444299999997</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="2">
         <v>129.06127699999999</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
         <v>5</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="1">
         <v>40</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="1">
         <v>0.8</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="1">
         <v>9.9</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="1">
         <v>0.4</v>
       </c>
-      <c r="F37">
-        <v>6.78</v>
-      </c>
-      <c r="G37">
+      <c r="F37" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G37" s="1">
         <v>1.505167513</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="1">
         <v>0.96039989800000003</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="1">
         <v>66.763991430000004</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38">
+      <c r="K37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
         <v>5</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="1">
         <v>40</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="1">
         <v>0.8</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="1">
         <v>9.9</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="1">
         <v>0.6</v>
       </c>
-      <c r="F38">
-        <v>6.78</v>
-      </c>
-      <c r="G38">
+      <c r="F38" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G38" s="1">
         <v>1.3952307989999999</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="1">
         <v>0.572882691</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="1">
         <v>103.7504326</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39">
+      <c r="K38" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
         <v>5</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="1">
         <v>55</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="1">
         <v>1</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="1">
         <v>9.9</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="1">
         <v>0.6</v>
       </c>
-      <c r="F39">
-        <v>6.78</v>
-      </c>
-      <c r="G39">
+      <c r="F39" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G39" s="1">
         <v>2.252865989</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="1">
         <v>0.87889271800000002</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="1">
         <v>109.1965845</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40">
+      <c r="K39" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
         <v>5</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="1">
+        <v>60</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="D40" s="1">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G40" s="1">
+        <v>1.879683529</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0.58028577599999998</v>
+      </c>
+      <c r="I40" s="1">
+        <v>137.99151180000001</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>5</v>
+      </c>
+      <c r="B41" s="1">
+        <v>65</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1</v>
+      </c>
+      <c r="D41" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G41" s="1">
+        <v>2.682374093</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0.92146893200000002</v>
+      </c>
+      <c r="I41" s="1">
+        <v>124.0075739</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>5</v>
+      </c>
+      <c r="B42" s="1">
+        <v>70</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="D42" s="1">
+        <v>49.9</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F42" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G42" s="1">
+        <v>4.3102209250000003</v>
+      </c>
+      <c r="H42" s="1">
+        <v>2.3026982290000002</v>
+      </c>
+      <c r="I42" s="1">
+        <v>79.739235260000001</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L42" s="1">
+        <v>2.2783000000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>5</v>
+      </c>
+      <c r="B43" s="1">
+        <v>75</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="D43" s="1">
+        <v>49.9</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G43" s="1">
+        <v>3.3586370140000001</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1.1302601029999999</v>
+      </c>
+      <c r="I43" s="1">
+        <v>126.58849429999999</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L43" s="1">
+        <v>1.0051000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>5</v>
+      </c>
+      <c r="B44" s="1">
+        <v>80</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1</v>
+      </c>
+      <c r="D44" s="1">
+        <v>89.9</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F44" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1.2524143860000001</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1.782394566</v>
+      </c>
+      <c r="I44" s="1">
+        <v>29.933242230000001</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L44" s="1">
+        <v>1.105</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>6</v>
+      </c>
+      <c r="B45" s="1">
+        <v>50</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="D45" s="1">
+        <v>29.9</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="F45" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G45" s="1">
+        <v>3.2376657541121001</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1.4939310061522799</v>
+      </c>
+      <c r="I45" s="1">
+        <v>92.323239055549806</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L45" s="1">
+        <v>1.5874999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>6</v>
+      </c>
+      <c r="B46" s="1">
+        <v>50</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="D46" s="1">
+        <v>89.9</v>
+      </c>
+      <c r="E46" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="F46" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G46" s="1">
+        <v>2.7807674889379199</v>
+      </c>
+      <c r="H46" s="1">
+        <v>1.47304764213508</v>
+      </c>
+      <c r="I46" s="1">
+        <v>80.418773691611193</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L46" s="1">
+        <v>1.3089</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>6</v>
+      </c>
+      <c r="B47" s="1">
+        <v>50</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="D47" s="1">
+        <v>89.9</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F47" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G47" s="1">
+        <v>2.53241125618172</v>
+      </c>
+      <c r="H47" s="1">
+        <v>1.48300191773088</v>
+      </c>
+      <c r="I47" s="1">
+        <v>72.744821879839904</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L47" s="1">
+        <v>1.1476999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>6</v>
+      </c>
+      <c r="B48" s="1">
+        <v>60</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="D48" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F48" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G48" s="1">
+        <v>5.3885781262674399</v>
+      </c>
+      <c r="H48" s="1">
+        <v>3.2962784551161501</v>
+      </c>
+      <c r="I48" s="1">
+        <v>69.640175067879696</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L48" s="1">
+        <v>3.1934</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>6</v>
+      </c>
+      <c r="B49" s="1">
+        <v>65</v>
+      </c>
+      <c r="C49" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="D49" s="1">
+        <v>49.9</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G49" s="1">
+        <v>2.9712475703487198</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0.95500345718013102</v>
+      </c>
+      <c r="I49" s="1">
+        <v>132.53892935910099</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>6</v>
+      </c>
+      <c r="B50" s="1">
+        <v>70</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D50" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="F50" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G50" s="1">
+        <v>5.9225877249741297</v>
+      </c>
+      <c r="H50" s="1">
+        <v>3.1760330185718901</v>
+      </c>
+      <c r="I50" s="1">
+        <v>79.439418351335803</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L50" s="1">
+        <v>3.0428999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>6</v>
+      </c>
+      <c r="B51" s="1">
+        <v>70</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="D51" s="1">
+        <v>49.9</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F51" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G51" s="1">
+        <v>6.5845068548894696</v>
+      </c>
+      <c r="H51" s="1">
+        <v>4.2136468193349801</v>
+      </c>
+      <c r="I51" s="1">
+        <v>66.569406556071399</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L51" s="1">
+        <v>4.2210999999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>7</v>
+      </c>
+      <c r="B52" s="1">
+        <v>45</v>
+      </c>
+      <c r="C52" s="1">
+        <v>1</v>
+      </c>
+      <c r="D52" s="1">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1.69672084667797</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0.63351696028414195</v>
+      </c>
+      <c r="I52" s="1">
+        <v>114.093712500572</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>7</v>
+      </c>
+      <c r="B53" s="1">
+        <v>50</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="D53" s="1">
+        <v>89.9</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="F53" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G53" s="1">
+        <v>2.0876896029905501</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0.79198719831059505</v>
+      </c>
+      <c r="I53" s="1">
+        <v>112.294200872516</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>7</v>
+      </c>
+      <c r="B54" s="1">
         <v>55</v>
       </c>
-      <c r="C40">
+      <c r="C54" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="D54" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="E54" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F54" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G54" s="1">
+        <v>3.0381115043517499</v>
+      </c>
+      <c r="H54" s="1">
+        <v>1.7040103415072201</v>
+      </c>
+      <c r="I54" s="1">
+        <v>75.952320207798294</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L54" s="1">
+        <v>1.0865</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>7</v>
+      </c>
+      <c r="B55" s="1">
+        <v>55</v>
+      </c>
+      <c r="C55" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="D55" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="E55" s="1">
         <v>1</v>
       </c>
-      <c r="D40">
-        <v>9.9</v>
-      </c>
-      <c r="E40">
+      <c r="F55" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G55" s="1">
+        <v>2.73509094999753</v>
+      </c>
+      <c r="H55" s="1">
+        <v>1.0074069773868899</v>
+      </c>
+      <c r="I55" s="1">
+        <v>115.658187000467</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L55" s="1">
+        <v>1.0416000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>7</v>
+      </c>
+      <c r="B56" s="1">
+        <v>70</v>
+      </c>
+      <c r="C56" s="1">
         <v>0.8</v>
       </c>
-      <c r="F40">
-        <v>6.78</v>
-      </c>
-      <c r="G40">
-        <v>2.1063673230000002</v>
-      </c>
-      <c r="H40">
-        <v>0.74556404899999995</v>
-      </c>
-      <c r="I40">
-        <v>120.35349669999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>5</v>
-      </c>
-      <c r="B41">
-        <v>60</v>
-      </c>
-      <c r="C41">
-        <v>1.2</v>
-      </c>
-      <c r="D41">
+      <c r="D56" s="1">
         <v>69.900000000000006</v>
       </c>
-      <c r="E41">
+      <c r="E56" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="F56" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G56" s="1">
+        <v>6.1258041495045497</v>
+      </c>
+      <c r="H56" s="1">
+        <v>3.1521430739765401</v>
+      </c>
+      <c r="I56" s="1">
+        <v>82.787877480661393</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L56" s="1">
+        <v>3.1206999999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>7</v>
+      </c>
+      <c r="B57" s="1">
+        <v>80</v>
+      </c>
+      <c r="C57" s="1">
         <v>1</v>
       </c>
-      <c r="F41">
-        <v>6.78</v>
-      </c>
-      <c r="G41">
-        <v>1.879683529</v>
-      </c>
-      <c r="H41">
-        <v>0.58028577599999998</v>
-      </c>
-      <c r="I41">
-        <v>137.99151180000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>5</v>
-      </c>
-      <c r="B42">
-        <v>65</v>
-      </c>
-      <c r="C42">
+      <c r="D57" s="1">
+        <v>49.9</v>
+      </c>
+      <c r="E57" s="1">
         <v>1</v>
       </c>
-      <c r="D42">
-        <v>9.9</v>
-      </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="F42">
-        <v>6.78</v>
-      </c>
-      <c r="G42">
-        <v>2.682374093</v>
-      </c>
-      <c r="H42">
-        <v>0.92146893200000002</v>
-      </c>
-      <c r="I42">
-        <v>124.0075739</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>5</v>
-      </c>
-      <c r="B43">
-        <v>70</v>
-      </c>
-      <c r="C43">
-        <v>0.4</v>
-      </c>
-      <c r="D43">
-        <v>49.9</v>
-      </c>
-      <c r="E43">
-        <v>0.4</v>
-      </c>
-      <c r="F43">
-        <v>6.78</v>
-      </c>
-      <c r="G43">
-        <v>4.3102209250000003</v>
-      </c>
-      <c r="H43">
-        <v>2.3026982290000002</v>
-      </c>
-      <c r="I43">
-        <v>79.739235260000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>5</v>
-      </c>
-      <c r="B44">
-        <v>75</v>
-      </c>
-      <c r="C44">
-        <v>0.8</v>
-      </c>
-      <c r="D44">
-        <v>49.9</v>
-      </c>
-      <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="F44">
-        <v>6.78</v>
-      </c>
-      <c r="G44">
-        <v>3.3586370140000001</v>
-      </c>
-      <c r="H44">
-        <v>1.1302601029999999</v>
-      </c>
-      <c r="I44">
-        <v>126.58849429999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>5</v>
-      </c>
-      <c r="B45">
-        <v>75</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45">
-        <v>49.9</v>
-      </c>
-      <c r="E45">
-        <v>1</v>
-      </c>
-      <c r="F45">
-        <v>6.78</v>
-      </c>
-      <c r="G45">
-        <v>3.1553097800000001</v>
-      </c>
-      <c r="H45">
-        <v>0.999283645</v>
-      </c>
-      <c r="I45">
-        <v>134.5125439</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>5</v>
-      </c>
-      <c r="B46">
-        <v>80</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46">
-        <v>89.9</v>
-      </c>
-      <c r="E46">
-        <v>0.8</v>
-      </c>
-      <c r="F46">
-        <v>6.78</v>
-      </c>
-      <c r="G46">
-        <v>1.2524143860000001</v>
-      </c>
-      <c r="H46">
-        <v>1.782394566</v>
-      </c>
-      <c r="I46">
-        <v>29.933242230000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>6</v>
-      </c>
-      <c r="B47">
-        <v>50</v>
-      </c>
-      <c r="C47">
-        <v>0.4</v>
-      </c>
-      <c r="D47">
-        <v>29.9</v>
-      </c>
-      <c r="E47">
-        <v>0.6</v>
-      </c>
-      <c r="F47">
-        <v>6.78</v>
-      </c>
-      <c r="G47">
-        <v>3.2376657541121001</v>
-      </c>
-      <c r="H47">
-        <v>1.4939310061522799</v>
-      </c>
-      <c r="I47">
-        <v>92.323239055549806</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>6</v>
-      </c>
-      <c r="B48">
-        <v>50</v>
-      </c>
-      <c r="C48">
-        <v>0.4</v>
-      </c>
-      <c r="D48">
-        <v>89.9</v>
-      </c>
-      <c r="E48">
-        <v>0.6</v>
-      </c>
-      <c r="F48">
-        <v>6.78</v>
-      </c>
-      <c r="G48">
-        <v>2.7807674889379199</v>
-      </c>
-      <c r="H48">
-        <v>1.47304764213508</v>
-      </c>
-      <c r="I48">
-        <v>80.418773691611193</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>6</v>
-      </c>
-      <c r="B49">
-        <v>50</v>
-      </c>
-      <c r="C49">
-        <v>0.4</v>
-      </c>
-      <c r="D49">
-        <v>89.9</v>
-      </c>
-      <c r="E49">
-        <v>0.8</v>
-      </c>
-      <c r="F49">
-        <v>6.78</v>
-      </c>
-      <c r="G49">
-        <v>2.53241125618172</v>
-      </c>
-      <c r="H49">
-        <v>1.48300191773088</v>
-      </c>
-      <c r="I49">
-        <v>72.744821879839904</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>6</v>
-      </c>
-      <c r="B50">
+      <c r="F57" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="G57" s="1">
+        <v>6.5432734498036504</v>
+      </c>
+      <c r="H57" s="1">
+        <v>2.8876869927254898</v>
+      </c>
+      <c r="I57" s="1">
+        <v>96.528268470475297</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C50">
-        <v>0.4</v>
-      </c>
-      <c r="D50">
-        <v>9.9</v>
-      </c>
-      <c r="E50">
-        <v>0.4</v>
-      </c>
-      <c r="F50">
-        <v>6.78</v>
-      </c>
-      <c r="G50">
-        <v>4.5578240580985199</v>
-      </c>
-      <c r="H50">
-        <v>2.62382820582698</v>
-      </c>
-      <c r="I50">
-        <v>74.000000440837198</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>6</v>
-      </c>
-      <c r="B51">
-        <v>60</v>
-      </c>
-      <c r="C51">
-        <v>0.4</v>
-      </c>
-      <c r="D51">
-        <v>9.9</v>
-      </c>
-      <c r="E51">
-        <v>0.4</v>
-      </c>
-      <c r="F51">
-        <v>6.78</v>
-      </c>
-      <c r="G51">
-        <v>5.3885781262674399</v>
-      </c>
-      <c r="H51">
-        <v>3.2962784551161501</v>
-      </c>
-      <c r="I51">
-        <v>69.640175067879696</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52">
-        <v>6</v>
-      </c>
-      <c r="B52">
-        <v>65</v>
-      </c>
-      <c r="C52">
-        <v>0.4</v>
-      </c>
-      <c r="D52">
-        <v>9.9</v>
-      </c>
-      <c r="E52">
-        <v>0.4</v>
-      </c>
-      <c r="F52">
-        <v>6.78</v>
-      </c>
-      <c r="G52">
-        <v>6.3410725156797199</v>
-      </c>
-      <c r="H52">
-        <v>4.1569921826908702</v>
-      </c>
-      <c r="I52">
-        <v>64.982000051632198</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A53">
-        <v>6</v>
-      </c>
-      <c r="B53">
-        <v>65</v>
-      </c>
-      <c r="C53">
-        <v>1.2</v>
-      </c>
-      <c r="D53">
-        <v>49.9</v>
-      </c>
-      <c r="E53">
-        <v>1</v>
-      </c>
-      <c r="F53">
-        <v>6.78</v>
-      </c>
-      <c r="G53">
-        <v>2.9712475703487198</v>
-      </c>
-      <c r="H53">
-        <v>0.95500345718013102</v>
-      </c>
-      <c r="I53">
-        <v>132.53892935910099</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A54">
-        <v>6</v>
-      </c>
-      <c r="B54">
-        <v>65</v>
-      </c>
-      <c r="C54">
-        <v>0.4</v>
-      </c>
-      <c r="D54">
-        <v>89.9</v>
-      </c>
-      <c r="E54">
-        <v>0.6</v>
-      </c>
-      <c r="F54">
-        <v>6.78</v>
-      </c>
-      <c r="G54">
-        <v>4.5085941764340998</v>
-      </c>
-      <c r="H54">
-        <v>4.7097250535323099</v>
-      </c>
-      <c r="I54">
-        <v>40.780744825646202</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A55">
-        <v>6</v>
-      </c>
-      <c r="B55">
-        <v>70</v>
-      </c>
-      <c r="C55">
-        <v>0.6</v>
-      </c>
-      <c r="D55">
-        <v>9.9</v>
-      </c>
-      <c r="E55">
-        <v>0.6</v>
-      </c>
-      <c r="F55">
-        <v>6.78</v>
-      </c>
-      <c r="G55">
-        <v>5.9225877249741297</v>
-      </c>
-      <c r="H55">
-        <v>3.1760330185718901</v>
-      </c>
-      <c r="I55">
-        <v>79.439418351335803</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A56">
-        <v>6</v>
-      </c>
-      <c r="B56">
-        <v>70</v>
-      </c>
-      <c r="C56">
-        <v>0.4</v>
-      </c>
-      <c r="D56">
-        <v>49.9</v>
-      </c>
-      <c r="E56">
-        <v>0.4</v>
-      </c>
-      <c r="F56">
-        <v>6.78</v>
-      </c>
-      <c r="G56">
-        <v>6.5845068548894696</v>
-      </c>
-      <c r="H56">
-        <v>4.2136468193349801</v>
-      </c>
-      <c r="I56">
-        <v>66.569406556071399</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A57">
-        <v>6</v>
-      </c>
-      <c r="B57">
-        <v>90</v>
-      </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57">
-        <v>9.9</v>
-      </c>
-      <c r="E57">
-        <v>0.4</v>
-      </c>
-      <c r="F57">
-        <v>6.78</v>
-      </c>
-      <c r="G57">
-        <v>11.731401090692801</v>
-      </c>
-      <c r="H57">
-        <v>12.425929348489399</v>
-      </c>
-      <c r="I57">
-        <v>40.218934939301803</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A58">
-        <v>7</v>
-      </c>
-      <c r="B58">
-        <v>45</v>
-      </c>
-      <c r="C58">
-        <v>1</v>
-      </c>
-      <c r="D58">
-        <v>69.900000000000006</v>
-      </c>
-      <c r="E58">
-        <v>1</v>
-      </c>
-      <c r="F58">
-        <v>6.78</v>
-      </c>
-      <c r="G58">
-        <v>1.69672084667797</v>
-      </c>
-      <c r="H58">
-        <v>0.63351696028414195</v>
-      </c>
-      <c r="I58">
-        <v>114.093712500572</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A59">
-        <v>7</v>
-      </c>
-      <c r="B59">
-        <v>50</v>
-      </c>
-      <c r="C59">
-        <v>0.8</v>
-      </c>
-      <c r="D59">
-        <v>89.9</v>
-      </c>
-      <c r="E59">
-        <v>1.2</v>
-      </c>
-      <c r="F59">
-        <v>6.78</v>
-      </c>
-      <c r="G59">
-        <v>2.0876896029905501</v>
-      </c>
-      <c r="H59">
-        <v>0.79198719831059505</v>
-      </c>
-      <c r="I59">
-        <v>112.294200872516</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A60">
-        <v>7</v>
-      </c>
-      <c r="B60">
-        <v>55</v>
-      </c>
-      <c r="C60">
-        <v>1.2</v>
-      </c>
-      <c r="D60">
-        <v>9.9</v>
-      </c>
-      <c r="E60">
-        <v>0.8</v>
-      </c>
-      <c r="F60">
-        <v>6.78</v>
-      </c>
-      <c r="G60">
-        <v>3.0381115043517499</v>
-      </c>
-      <c r="H60">
-        <v>1.7040103415072201</v>
-      </c>
-      <c r="I60">
-        <v>75.952320207798294</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A61">
-        <v>7</v>
-      </c>
-      <c r="B61">
-        <v>55</v>
-      </c>
-      <c r="C61">
-        <v>1.2</v>
-      </c>
-      <c r="D61">
-        <v>9.9</v>
-      </c>
-      <c r="E61">
-        <v>1</v>
-      </c>
-      <c r="F61">
-        <v>6.78</v>
-      </c>
-      <c r="G61">
-        <v>2.73509094999753</v>
-      </c>
-      <c r="H61">
-        <v>1.0074069773868899</v>
-      </c>
-      <c r="I61">
-        <v>115.658187000467</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A62">
-        <v>7</v>
-      </c>
-      <c r="B62">
-        <v>70</v>
-      </c>
-      <c r="C62">
-        <v>0.8</v>
-      </c>
-      <c r="D62">
-        <v>69.900000000000006</v>
-      </c>
-      <c r="E62">
-        <v>0.6</v>
-      </c>
-      <c r="F62">
-        <v>6.78</v>
-      </c>
-      <c r="G62">
-        <v>6.1258041495045497</v>
-      </c>
-      <c r="H62">
-        <v>3.1521430739765401</v>
-      </c>
-      <c r="I62">
-        <v>82.787877480661393</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A63">
-        <v>7</v>
-      </c>
-      <c r="B63">
-        <v>80</v>
-      </c>
-      <c r="C63">
-        <v>1</v>
-      </c>
-      <c r="D63">
-        <v>49.9</v>
-      </c>
-      <c r="E63">
-        <v>1</v>
-      </c>
-      <c r="F63">
-        <v>6.78</v>
-      </c>
-      <c r="G63">
-        <v>6.5432734498036504</v>
-      </c>
-      <c r="H63">
-        <v>2.8876869927254898</v>
-      </c>
-      <c r="I63">
-        <v>96.528268470475297</v>
+      <c r="L57" s="1">
+        <v>2.9068999999999998</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="A47:I57">
+  <conditionalFormatting sqref="A45:I51 L50:L51 L45:L48">
     <cfRule type="expression" dxfId="1" priority="21">
-      <formula>#REF!*0.9&gt;$H47</formula>
+      <formula>#REF!*0.9&gt;$H45</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="22">
-      <formula>#REF!*1.05&lt;$G47</formula>
+      <formula>#REF!*1.05&lt;$G45</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
